--- a/docs/importance_by_type.xlsx
+++ b/docs/importance_by_type.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,71 +416,91 @@
   </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sd</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>daymin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>daymax</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>w1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>w2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>w3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>w4</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ranks</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>pFin</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Recent</t>
         </is>
@@ -514,22 +523,22 @@
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>02/01/2004</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>2/1/4</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>0/0/7</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>0/0/7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>0/0/10</t>
         </is>
@@ -537,14 +546,14 @@
       <c r="L2" t="n">
         <v>75.26000000000001</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>0.00E+00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
@@ -567,22 +576,22 @@
       <c r="G3" t="n">
         <v>31</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>05/02/2000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>5/2/0</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>7/0/0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>7/0/0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>10/0/0</t>
         </is>
@@ -590,14 +599,14 @@
       <c r="L3" t="n">
         <v>17.13</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> NA</t>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Calendar</t>
         </is>
@@ -609,33 +618,33 @@
         <v>0.00082</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000446</v>
+        <v>0.000447</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00371</v>
+        <v>0.00373</v>
       </c>
       <c r="G4" t="n">
         <v>26</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>0/4/3</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>0/7/0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>0/7/0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>0/10/0</t>
         </is>
@@ -643,7 +652,7 @@
       <c r="L4" t="n">
         <v>48.61</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>4.38E-06</t>
         </is>

--- a/docs/importance_by_type.xlsx
+++ b/docs/importance_by_type.xlsx
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00143</v>
+        <v>0.00144</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00203</v>
+        <v>0.00209</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000625</v>
+        <v>0.000641</v>
       </c>
       <c r="E2" t="n">
         <v>31</v>
@@ -562,10 +562,10 @@
         <v>0.0114</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00249</v>
+        <v>0.00256</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000549</v>
+        <v>0.000509</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -612,19 +612,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00279</v>
+        <v>0.00281</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00082</v>
+        <v>0.000813</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000447</v>
+        <v>0.000466</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00373</v>
+        <v>0.00376</v>
       </c>
       <c r="G4" t="n">
         <v>26</v>
